--- a/data/trans_camb/P19-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,56; -0,78</t>
+          <t>-7,6; -0,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 0,64</t>
+          <t>-7,11; 0,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 0,9</t>
+          <t>-6,85; 1,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 3,59</t>
+          <t>-2,72; 3,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 4,82</t>
+          <t>-3,07; 4,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,74; -2,24</t>
+          <t>-8,58; -2,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,23</t>
+          <t>-3,93; 0,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 1,63</t>
+          <t>-3,73; 1,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -1,88</t>
+          <t>-7,0; -2,09</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,89; -4,11</t>
+          <t>-33,97; -2,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 3,49</t>
+          <t>-31,35; 1,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 4,67</t>
+          <t>-31,17; 7,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 17,11</t>
+          <t>-11,44; 18,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 22,68</t>
+          <t>-12,58; 20,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,12; -10,74</t>
+          <t>-35,72; -12,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 6,08</t>
+          <t>-17,22; 4,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 7,93</t>
+          <t>-16,96; 6,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-30,34; -9,15</t>
+          <t>-30,5; -9,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,94</t>
+          <t>-2,76; 3,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 8,1</t>
+          <t>2,47; 8,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 2,51</t>
+          <t>-9,31; 2,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,56; -0,62</t>
+          <t>-7,35; -0,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 4,24</t>
+          <t>-2,33; 4,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,84; -2,81</t>
+          <t>-16,11; -2,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 0,37</t>
+          <t>-4,06; 0,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,76</t>
+          <t>1,2; 5,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,73; -0,68</t>
+          <t>-10,17; -1,05</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 12,17</t>
+          <t>-10,07; 12,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,22; 33,79</t>
+          <t>8,77; 34,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,36; 9,66</t>
+          <t>-35,63; 9,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,49; -1,85</t>
+          <t>-19,15; -2,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 12,07</t>
+          <t>-6,03; 11,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,49; -7,65</t>
+          <t>-42,74; -6,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 1,21</t>
+          <t>-12,59; 1,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 19,3</t>
+          <t>3,75; 19,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,72; -2,25</t>
+          <t>-32,2; -3,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 11,96</t>
+          <t>-0,71; 11,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 14,15</t>
+          <t>1,94; 13,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 10,73</t>
+          <t>-1,05; 10,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 10,74</t>
+          <t>-2,61; 10,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 10,62</t>
+          <t>-1,71; 10,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 14,77</t>
+          <t>3,43; 14,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 9,88</t>
+          <t>0,79; 9,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 11,18</t>
+          <t>2,2; 10,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 10,8</t>
+          <t>3,58; 11,49</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 43,04</t>
+          <t>-2,35; 41,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,89; 51,59</t>
+          <t>5,87; 51,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 38,6</t>
+          <t>-3,08; 38,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 32,15</t>
+          <t>-6,39; 31,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 32,0</t>
+          <t>-4,12; 31,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,56; 46,16</t>
+          <t>8,34; 44,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,44; 31,55</t>
+          <t>2,61; 31,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,43; 35,35</t>
+          <t>6,18; 34,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,86; 34,36</t>
+          <t>9,92; 36,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,9</t>
+          <t>-2,31; 2,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,49</t>
+          <t>2,12; 6,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 3,06</t>
+          <t>-5,32; 3,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,24</t>
+          <t>-3,45; 1,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,57</t>
+          <t>0,9; 5,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 1,56</t>
+          <t>-7,2; 1,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,96</t>
+          <t>-2,2; 0,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,19</t>
+          <t>2,16; 5,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,89</t>
+          <t>-4,44; 1,79</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 7,83</t>
+          <t>-9,03; 9,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,59; 27,28</t>
+          <t>7,93; 27,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,36; 12,52</t>
+          <t>-20,69; 12,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 4,09</t>
+          <t>-10,71; 3,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 18,99</t>
+          <t>2,8; 18,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,74; 5,16</t>
+          <t>-22,74; 5,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 3,52</t>
+          <t>-7,63; 3,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,31; 19,13</t>
+          <t>7,4; 19,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 6,78</t>
+          <t>-15,56; 6,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,98</t>
+          <t>-3,84</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,64</t>
+          <t>-5,72</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,49</t>
+          <t>-4,89</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,6; -0,48</t>
+          <t>-7,63; -0,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 0,27</t>
+          <t>-7,22; -0,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 1,23</t>
+          <t>-7,9; 0,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 3,67</t>
+          <t>-2,77; 3,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 4,36</t>
+          <t>-2,93; 4,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,58; -2,55</t>
+          <t>-8,68; -2,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 0,88</t>
+          <t>-3,83; 1,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 1,29</t>
+          <t>-3,7; 1,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,0; -2,09</t>
+          <t>-7,31; -2,47</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-14,5%</t>
+          <t>-18,7%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-25,03%</t>
+          <t>-25,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-20,74%</t>
+          <t>-22,59%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,97; -2,18</t>
+          <t>-33,35; -2,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,35; 1,64</t>
+          <t>-32,55; -0,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 7,3</t>
+          <t>-35,95; -0,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 18,13</t>
+          <t>-11,34; 17,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 20,26</t>
+          <t>-12,31; 19,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,72; -12,16</t>
+          <t>-35,72; -13,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 4,24</t>
+          <t>-16,71; 5,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 6,35</t>
+          <t>-16,19; 8,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-30,5; -9,91</t>
+          <t>-32,13; -12,23</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,5</t>
+          <t>-5,18</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,52</t>
+          <t>-2,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 3,0</t>
+          <t>-2,64; 3,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 8,41</t>
+          <t>2,44; 8,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 2,39</t>
+          <t>-3,06; 3,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,35; -0,85</t>
+          <t>-7,46; -0,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 4,19</t>
+          <t>-2,31; 4,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,11; -2,33</t>
+          <t>-8,42; -2,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,34</t>
+          <t>-4,05; 0,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,81</t>
+          <t>1,12; 5,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,17; -1,05</t>
+          <t>-4,6; -0,27</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-7,13%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-20,27%</t>
+          <t>-14,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-14,51%</t>
+          <t>-7,66%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 12,47</t>
+          <t>-9,87; 12,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 34,42</t>
+          <t>9,07; 36,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 9,82</t>
+          <t>-11,24; 12,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,15; -2,4</t>
+          <t>-19,27; -2,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 11,76</t>
+          <t>-5,89; 12,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,74; -6,59</t>
+          <t>-21,59; -6,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 1,17</t>
+          <t>-12,5; 1,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 19,24</t>
+          <t>3,76; 19,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-32,2; -3,5</t>
+          <t>-14,18; -0,94</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,91</t>
+          <t>5,08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,01</t>
+          <t>8,19</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,24</t>
+          <t>6,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 11,77</t>
+          <t>-0,41; 11,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 13,83</t>
+          <t>1,9; 13,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 10,64</t>
+          <t>-0,41; 11,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 10,68</t>
+          <t>-2,37; 11,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 10,55</t>
+          <t>-1,62; 10,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 14,86</t>
+          <t>2,97; 13,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 9,85</t>
+          <t>0,89; 9,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 10,8</t>
+          <t>2,11; 10,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 11,49</t>
+          <t>2,98; 10,69</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 41,57</t>
+          <t>-1,45; 41,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,87; 51,26</t>
+          <t>5,52; 48,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 38,91</t>
+          <t>-1,25; 41,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 31,96</t>
+          <t>-5,95; 33,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 31,4</t>
+          <t>-4,19; 32,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,34; 44,42</t>
+          <t>7,33; 41,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,61; 31,86</t>
+          <t>2,55; 31,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,18; 34,17</t>
+          <t>5,68; 35,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,92; 36,26</t>
+          <t>8,29; 34,14</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,18</t>
+          <t>-2,4; 1,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,41</t>
+          <t>2,14; 6,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 3,02</t>
+          <t>-1,11; 3,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,19</t>
+          <t>-3,29; 1,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,41</t>
+          <t>0,8; 5,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 1,84</t>
+          <t>-2,35; 2,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,97</t>
+          <t>-2,28; 0,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,24</t>
+          <t>2,02; 5,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 1,79</t>
+          <t>-0,94; 2,15</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-4,67%</t>
+          <t>-0,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 9,31</t>
+          <t>-9,31; 7,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,93; 27,38</t>
+          <t>8,3; 27,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 12,56</t>
+          <t>-4,17; 16,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 3,93</t>
+          <t>-10,0; 3,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,8; 18,05</t>
+          <t>2,52; 17,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 5,81</t>
+          <t>-7,2; 6,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 3,51</t>
+          <t>-7,78; 3,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,4; 19,16</t>
+          <t>7,06; 19,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 6,41</t>
+          <t>-3,19; 7,89</t>
         </is>
       </c>
     </row>
